--- a/data/trans_orig/IP1011-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1011-Clase-trans_orig.xlsx
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>198543</t>
+          <t>198595</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399007</t>
+          <t>398592</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71757</t>
+          <t>71893</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68972</t>
+          <t>69387</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>143030</t>
+          <t>143011</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>634872</t>
+          <t>635359</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>680598</t>
+          <t>680524</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1318394</t>
+          <t>1318243</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85881</t>
+          <t>85952</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174769</t>
+          <t>175487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48735</t>
+          <t>49105</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>123147</t>
+          <t>122950</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>669445</t>
+          <t>669432</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>710417</t>
+          <t>710120</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1381376</t>
+          <t>1381899</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1386926</t>
+          <t>1386927</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>207780</t>
+          <t>207980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>430851</t>
+          <t>431181</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>706180</t>
+          <t>706157</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1376944</t>
+          <t>1377408</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/IP1011-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1011-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1183,42 +1183,42 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1296,52 +1296,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3479</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3790</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4215</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1869,67 +1869,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>201374</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>198537</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>201374</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>198595</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398592</t>
+          <t>399017</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2207,47 +2207,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>104120</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2442,102 +2442,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3216</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>605</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2977</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,81%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3005</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>4,05%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4231</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1207</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4251</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -2550,74 +2550,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>71790</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>69176</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>95,56%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>74265</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>71893</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>71841</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>99,19%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>95,95%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>71790</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>69387</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>95,85%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>217</t>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>143011</t>
+          <t>143031</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4598</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3497</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2930</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4079</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -2893,74 +2893,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1027</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>683300</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>680005</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>952</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>638251</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>635359</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>635926</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1027</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>683300</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>680524</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1979</t>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1318243</t>
+          <t>1318366</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,107 +3357,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>672</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>672</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3811</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2716</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -3470,72 +3470,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89091</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>86239</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>89091</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>85952</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>175487</t>
+          <t>174829</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3813,47 +3813,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4156,47 +4156,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4499,47 +4499,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>205628</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4842,47 +4842,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5072,107 +5072,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1412</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4806</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4910</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1412</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4913</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1412</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4999</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -5185,74 +5185,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>52499</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>49105</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>49001</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>97,38%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>91,09%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>90,89%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>181</t>
@@ -5265,7 +5265,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122950</t>
+          <t>123036</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4206</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1412</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4649</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4440</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3381</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -5528,74 +5528,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>712829</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>709295</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,41%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>971</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>672669</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>669432</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>669641</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,79%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>712829</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>710120</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1988</t>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1381899</t>
+          <t>1381340</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1386927</t>
+          <t>1386926</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6105,47 +6105,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6448,47 +6448,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6791,47 +6791,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,107 +7021,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>713</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2874</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3580</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3250</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>210141</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>207239</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>210141</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>207980</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>431181</t>
+          <t>430851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7477,47 +7477,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7820,47 +7820,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,107 +8050,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>713</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3580</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3584</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3831</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>709024</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>706148</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>709024</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>706157</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1377408</t>
+          <t>1377655</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
